--- a/Unity/Assets/Config/Excel/TaskConfig.xlsx
+++ b/Unity/Assets/Config/Excel/TaskConfig.xlsx
@@ -137,7 +137,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N3" authorId="0">
+    <comment ref="M3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -172,7 +172,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="55">
   <si>
     <t>##var</t>
   </si>
@@ -198,7 +198,7 @@
     <t>TaskGold</t>
   </si>
   <si>
-    <t>ItemID</t>
+    <t>RewardItem</t>
   </si>
   <si>
     <t>TargetType</t>
@@ -210,9 +210,6 @@
     <t>TargetValue</t>
   </si>
   <si>
-    <t>ItemNum</t>
-  </si>
-  <si>
     <t>TaskDes</t>
   </si>
   <si>
@@ -225,6 +222,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>(array#sep=@),rewardItem</t>
+  </si>
+  <si>
     <t>TaskTargetType</t>
   </si>
   <si>
@@ -264,55 +264,76 @@
     <t>目标值</t>
   </si>
   <si>
-    <t>奖励道具数量</t>
-  </si>
-  <si>
     <t>任务描述</t>
   </si>
   <si>
     <t>达到1级</t>
   </si>
   <si>
+    <t>10002001;1</t>
+  </si>
+  <si>
     <t>升级到1级</t>
   </si>
   <si>
     <t>杀5只怪</t>
   </si>
   <si>
+    <t>10002002;1</t>
+  </si>
+  <si>
     <t>击杀任意5只怪物</t>
   </si>
   <si>
     <t>达到3级</t>
   </si>
   <si>
+    <t>10002003;1</t>
+  </si>
+  <si>
     <t>升级到3级</t>
   </si>
   <si>
     <t>杀一个Boss</t>
   </si>
   <si>
+    <t>10002004;1</t>
+  </si>
+  <si>
     <t>击杀任意一只Boss</t>
   </si>
   <si>
     <t>杀一个哥布林</t>
   </si>
   <si>
+    <t>10002005;1</t>
+  </si>
+  <si>
     <t>击杀一只哥布林</t>
   </si>
   <si>
     <t>战力达到100</t>
   </si>
   <si>
+    <t>10002006;1</t>
+  </si>
+  <si>
     <t>提升战力到100</t>
   </si>
   <si>
     <t>达到5级</t>
   </si>
   <si>
+    <t>10003001;1</t>
+  </si>
+  <si>
     <t>升级到5级</t>
   </si>
   <si>
     <t>战力达到200</t>
+  </si>
+  <si>
+    <t>10003002;1</t>
   </si>
   <si>
     <t>提升战力到200</t>
@@ -1402,16 +1423,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
     <col min="2" max="2" width="15.625" style="3" customWidth="1"/>
-    <col min="3" max="13" width="15.625" customWidth="1"/>
-    <col min="14" max="14" width="30.625" customWidth="1"/>
+    <col min="3" max="8" width="15.625" customWidth="1"/>
+    <col min="9" max="9" width="22.625" customWidth="1"/>
+    <col min="10" max="12" width="15.625" customWidth="1"/>
+    <col min="13" max="13" width="30.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
+    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1451,34 +1474,31 @@
       <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
+      <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="D2" s="5" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>16</v>
@@ -1493,13 +1513,10 @@
         <v>18</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
+    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -1539,16 +1556,13 @@
       <c r="M3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="6" t="s">
-        <v>31</v>
-      </c>
     </row>
-    <row r="4" s="2" customFormat="1" ht="16.5" spans="2:14">
+    <row r="4" s="2" customFormat="1" ht="16.5" spans="2:13">
       <c r="B4" s="2">
         <v>10010000</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -1565,8 +1579,8 @@
       <c r="H4" s="2">
         <v>20</v>
       </c>
-      <c r="I4" s="2">
-        <v>10002001</v>
+      <c r="I4" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="J4" s="2">
         <v>1</v>
@@ -1577,14 +1591,11 @@
       <c r="L4" s="2">
         <v>1</v>
       </c>
-      <c r="M4" s="2">
-        <v>1</v>
-      </c>
-      <c r="N4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" ht="16.5" spans="2:14">
+    <row r="5" ht="16.5" spans="2:13">
       <c r="B5" s="2">
         <v>10010001</v>
       </c>
@@ -1606,8 +1617,8 @@
       <c r="H5" s="2">
         <v>20</v>
       </c>
-      <c r="I5" s="2">
-        <v>10002002</v>
+      <c r="I5" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="J5" s="8">
         <v>2</v>
@@ -1618,19 +1629,16 @@
       <c r="L5" s="8">
         <v>5</v>
       </c>
-      <c r="M5" s="8">
-        <v>1</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>35</v>
+      <c r="M5" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="2:14">
+    <row r="6" ht="16.5" spans="2:13">
       <c r="B6" s="2">
         <v>10010002</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
@@ -1647,8 +1655,8 @@
       <c r="H6" s="2">
         <v>20</v>
       </c>
-      <c r="I6" s="2">
-        <v>10002003</v>
+      <c r="I6" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="J6" s="8">
         <v>1</v>
@@ -1659,19 +1667,16 @@
       <c r="L6" s="8">
         <v>3</v>
       </c>
-      <c r="M6" s="8">
-        <v>1</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>37</v>
+      <c r="M6" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="2:14">
+    <row r="7" ht="16.5" spans="2:13">
       <c r="B7" s="2">
         <v>10010003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
@@ -1688,8 +1693,8 @@
       <c r="H7" s="2">
         <v>20</v>
       </c>
-      <c r="I7" s="2">
-        <v>10002004</v>
+      <c r="I7" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="J7" s="9">
         <v>3</v>
@@ -1700,19 +1705,16 @@
       <c r="L7" s="9">
         <v>1</v>
       </c>
-      <c r="M7" s="8">
-        <v>1</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>39</v>
+      <c r="M7" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="2:14">
+    <row r="8" ht="16.5" spans="2:13">
       <c r="B8" s="2">
         <v>10010004</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
@@ -1729,8 +1731,8 @@
       <c r="H8" s="2">
         <v>20</v>
       </c>
-      <c r="I8" s="2">
-        <v>10002005</v>
+      <c r="I8" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="J8" s="9">
         <v>4</v>
@@ -1741,19 +1743,16 @@
       <c r="L8" s="9">
         <v>1</v>
       </c>
-      <c r="M8" s="8">
-        <v>1</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>41</v>
+      <c r="M8" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="2:14">
+    <row r="9" ht="16.5" spans="2:13">
       <c r="B9" s="2">
         <v>10010005</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D9" s="8">
         <v>1</v>
@@ -1770,8 +1769,8 @@
       <c r="H9" s="2">
         <v>20</v>
       </c>
-      <c r="I9" s="2">
-        <v>10002006</v>
+      <c r="I9" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="J9" s="9">
         <v>6</v>
@@ -1782,19 +1781,16 @@
       <c r="L9" s="9">
         <v>100</v>
       </c>
-      <c r="M9" s="8">
-        <v>1</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>43</v>
+      <c r="M9" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="10" ht="16.5" spans="2:14">
+    <row r="10" ht="16.5" spans="2:13">
       <c r="B10" s="2">
         <v>10010006</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D10" s="8">
         <v>1</v>
@@ -1811,8 +1807,8 @@
       <c r="H10" s="2">
         <v>20</v>
       </c>
-      <c r="I10" s="8">
-        <v>10003001</v>
+      <c r="I10" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="J10" s="9">
         <v>1</v>
@@ -1823,19 +1819,16 @@
       <c r="L10" s="9">
         <v>5</v>
       </c>
-      <c r="M10" s="8">
-        <v>1</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>45</v>
+      <c r="M10" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="11" ht="16.5" spans="2:14">
+    <row r="11" ht="16.5" spans="2:13">
       <c r="B11" s="2">
         <v>10010007</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D11" s="8">
         <v>1</v>
@@ -1852,8 +1845,8 @@
       <c r="H11" s="2">
         <v>20</v>
       </c>
-      <c r="I11" s="8">
-        <v>10003002</v>
+      <c r="I11" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="J11" s="9">
         <v>6</v>
@@ -1864,11 +1857,8 @@
       <c r="L11" s="9">
         <v>200</v>
       </c>
-      <c r="M11" s="8">
-        <v>1</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>47</v>
+      <c r="M11" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="4:4">

--- a/Unity/Assets/Config/Excel/TaskConfig.xlsx
+++ b/Unity/Assets/Config/Excel/TaskConfig.xlsx
@@ -204,7 +204,7 @@
     <t>TargetType</t>
   </si>
   <si>
-    <t>Target</t>
+    <t>TargetId</t>
   </si>
   <si>
     <t>TargetValue</t>
@@ -349,7 +349,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -377,13 +377,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -528,19 +521,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -926,151 +912,151 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
